--- a/SMEnterprise/Content/Uploads/StudentList-Upload1.xlsx
+++ b/SMEnterprise/Content/Uploads/StudentList-Upload1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12495"/>
+    <workbookView windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet11" sheetId="17" r:id="rId1"/>
@@ -12,12 +12,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet11!$A$1:$Q$6</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="229">
   <si>
     <t>S.No.</t>
   </si>
@@ -70,302 +83,654 @@
     <t>MiniAddress</t>
   </si>
   <si>
-    <t>8/13</t>
+    <t>DBS/ 1709/15</t>
   </si>
   <si>
-    <t>ANNU KUMARI</t>
+    <t>KANGKILING PERTIN</t>
   </si>
   <si>
-    <t>SHAMBHU SAHU</t>
+    <t>Noyaram Pertin</t>
   </si>
   <si>
-    <t>ANITA DEVI</t>
+    <t>Yarek Pertin</t>
   </si>
   <si>
-    <t>29/09/2010</t>
+    <t>Bosi Didum</t>
   </si>
   <si>
-    <t>5933 2623 2968</t>
+    <t>DBS/1478/16</t>
   </si>
   <si>
-    <t>WARD 4</t>
+    <t>ARADHYA SINGH</t>
   </si>
   <si>
-    <t>12/13</t>
+    <t>Harandra Singh</t>
   </si>
   <si>
-    <t>GUNJA KUMARI</t>
+    <t>Ranju Singh</t>
   </si>
   <si>
-    <t>VIJAY SAH</t>
+    <t>sawmill area</t>
   </si>
   <si>
-    <t>MAMTA DEVI</t>
+    <t>DBS/ 2220/05</t>
   </si>
   <si>
-    <t>10/08/2010</t>
+    <t>AYUSH RAJ</t>
   </si>
   <si>
-    <t>9/13</t>
+    <t>Mukesh Ray</t>
   </si>
   <si>
-    <t>PRITI KUMARI</t>
+    <t>Rinku Ray</t>
   </si>
   <si>
-    <t>RAJU SAH</t>
+    <t>DBS/1343/15</t>
   </si>
   <si>
-    <t>ASHA DEVI</t>
+    <t>KALINAM BORANG</t>
   </si>
   <si>
-    <t>25/10/2010</t>
+    <t>lungsa Borang</t>
   </si>
   <si>
-    <t>RAM CHOWK</t>
+    <t>Ogul Boran</t>
   </si>
   <si>
-    <t>44/13</t>
+    <t>High Region</t>
   </si>
   <si>
-    <t>ABHISHEK KUMAR</t>
+    <t>DBS/1344/15</t>
   </si>
   <si>
-    <t>MANOJ KUMAR</t>
+    <t>OMEY TAPAK</t>
   </si>
   <si>
-    <t>RANJU DEVI</t>
+    <t>Anand Tapak</t>
   </si>
   <si>
-    <t>22/10/2010</t>
+    <t>Yanoti Tapak</t>
   </si>
   <si>
-    <t>MOHNA</t>
+    <t>jarkong</t>
   </si>
   <si>
-    <t>77/13</t>
+    <t>DBS/ 1326/15</t>
   </si>
   <si>
-    <t>OM KUMAR</t>
+    <t>MAAN CHETTRY</t>
   </si>
   <si>
-    <t>PAWAN KAMAT</t>
+    <t>Dhan Bdr. Chettry</t>
   </si>
   <si>
-    <t>SHILA DEVI</t>
+    <t>Munu Chettry</t>
   </si>
   <si>
-    <t>19/08/2010</t>
+    <t>DBS/1339/15</t>
   </si>
   <si>
-    <t>WARD 3</t>
+    <t>AKRITI PANDIT</t>
   </si>
   <si>
-    <t>25/13</t>
+    <t>Lt. Dinesh Pandit</t>
   </si>
   <si>
-    <t>NEHA KUMARI</t>
+    <t>Seema Pandit</t>
   </si>
   <si>
-    <t>DURGESH MISHRA</t>
+    <t>CHF Psg</t>
   </si>
   <si>
-    <t>KUMKUM MISHRA</t>
+    <t>DBS/2190/21</t>
   </si>
   <si>
-    <t>01/10/2009</t>
+    <t>TELYON MIYU</t>
   </si>
   <si>
-    <t>LANGRA CHOWK</t>
+    <t>Ratsung Miyu</t>
   </si>
   <si>
-    <t>58/14</t>
+    <t>Aliyang Miyu</t>
   </si>
   <si>
-    <t>SWATI MUKESH KUNWAR</t>
+    <t>Gumin Nagar</t>
   </si>
   <si>
-    <t>MUKESH KUNWAR</t>
+    <t>DBS/ 2270/56/22</t>
   </si>
   <si>
-    <t>JYOTI DEVI</t>
+    <t>GERIK ANGEL KAKKI</t>
   </si>
   <si>
-    <t>08/04/2010</t>
+    <t>Kirgam Kakki</t>
   </si>
   <si>
-    <t>WARD 13</t>
+    <t>Margam Kakki</t>
   </si>
   <si>
-    <t>36/15</t>
+    <t>DBS/1128/14</t>
   </si>
   <si>
-    <t>SHAIL KUMARI</t>
+    <t>NEHA SONAR</t>
   </si>
   <si>
-    <t>PRADEEP KR YADAV</t>
+    <t>Monuj Sonar</t>
   </si>
   <si>
-    <t>02/07/2010</t>
+    <t>Deepa sonar</t>
   </si>
   <si>
-    <t>COURT CHOWK</t>
+    <t>DBS/ 1408/15</t>
   </si>
   <si>
-    <t>71/13</t>
+    <t>SUMPI TALOH</t>
   </si>
   <si>
-    <t>SHEETAL KUMARI</t>
+    <t>Brigadeer Taloh</t>
   </si>
   <si>
-    <t>DILIP CHAUDHARY</t>
+    <t>Aroti Taloh</t>
   </si>
   <si>
-    <t>17/09/2010</t>
+    <t>DBS/2784/55/24</t>
   </si>
   <si>
-    <t>18/14</t>
+    <t>NONGKI DANGGEN</t>
   </si>
   <si>
-    <t>SHILPI KUMARI</t>
+    <t xml:space="preserve">Dipu Danggen </t>
   </si>
   <si>
-    <t>ARUN KUMAR</t>
+    <t>Robita Danggen</t>
   </si>
   <si>
-    <t>JYOTISHNA DEVI</t>
+    <t>DBS/ 1608/16</t>
   </si>
   <si>
-    <t>12/11/2010</t>
+    <t>ASENG PARON</t>
   </si>
   <si>
-    <t>38/13</t>
+    <t>Orik Paron</t>
   </si>
   <si>
-    <t>SUNITI PRABHA</t>
+    <t>Omik Paron</t>
   </si>
   <si>
-    <t>RAJ KUMAR PRASAD</t>
+    <t>2mile area</t>
   </si>
   <si>
-    <t>LALITA DEVI</t>
+    <t>DBS/ 2785/56/24</t>
   </si>
   <si>
-    <t>06/02/2010</t>
+    <t>TATULUNG PADUNG</t>
   </si>
   <si>
-    <t>BELARAHI</t>
+    <t>Odang Padung</t>
   </si>
   <si>
-    <t>43/13</t>
+    <t>Omoty Padung</t>
   </si>
   <si>
-    <t>ABHIJEET KUMAR</t>
+    <t>Kebang</t>
   </si>
   <si>
-    <t>MANOJ KUMAR SAH</t>
+    <t>DBS/2022/20</t>
   </si>
   <si>
-    <t>94/14</t>
+    <t>SUMAN PRADHAN</t>
   </si>
   <si>
-    <t>ARVIND KUMAR</t>
+    <t>Rajiv Pradhan</t>
   </si>
   <si>
-    <t>BIRENDRA KUMAR</t>
+    <t>Pinky Pradhan</t>
   </si>
   <si>
-    <t>SIKWIL DEVI</t>
+    <t>Mirmir Tinali</t>
   </si>
   <si>
-    <t>05/08/2010</t>
+    <t>DBS/ 2035/20</t>
   </si>
   <si>
-    <t>9274 8051 1704</t>
+    <t>LIDIYA NORAM</t>
   </si>
   <si>
-    <t>PANCHANATH</t>
+    <t>Tadang Noram</t>
   </si>
   <si>
-    <t>22/18</t>
+    <t>Yamen Taki</t>
   </si>
   <si>
-    <t>HARSH KUMAR</t>
+    <t>Rottung</t>
   </si>
   <si>
-    <t>SHIV SHAMBHU PANJIYAR</t>
+    <t>DBS/ 1335/15</t>
   </si>
   <si>
-    <t>RAJNI KUMARI</t>
+    <t>NIDHI CHETTRY</t>
   </si>
   <si>
-    <t>28/11/2010</t>
+    <t>Raju Chettry</t>
   </si>
   <si>
-    <t>CHANAURA GANJ</t>
+    <t>yatam Kakki</t>
   </si>
   <si>
-    <t>65/13</t>
+    <t>DBS/1409/15</t>
   </si>
   <si>
-    <t>SWEETA KUMARI</t>
+    <t>RITUL NAMASUDRA</t>
   </si>
   <si>
-    <t>JITENDRA PRASAD</t>
+    <t>Babul Namasudra</t>
   </si>
   <si>
-    <t>02/04/2010</t>
+    <t>Sojola Namasudra</t>
   </si>
   <si>
-    <t>BIBHU ANSHUMAN</t>
+    <t>DBS/ 1344/15</t>
   </si>
   <si>
-    <t>HANUMAN PRASAD</t>
+    <t>OYAMSU PERTIN</t>
   </si>
   <si>
-    <t>NUTAN GUPTA</t>
+    <t>Yalom Pertin</t>
   </si>
   <si>
-    <t>05/10/2010</t>
+    <t>Aman Modi</t>
   </si>
   <si>
-    <t>SHIVAM KUMAR JHA</t>
+    <t>DBS/ 2799/70/24</t>
   </si>
   <si>
-    <t>MANOJ KUMAR JHA</t>
+    <t>DITTE TAMIR</t>
   </si>
   <si>
-    <t>SEEMA JHA</t>
+    <t>Tasong Tamir</t>
   </si>
   <si>
-    <t>24/01/2009</t>
+    <t>Osi Tadeng Tamir</t>
   </si>
   <si>
-    <t>SUMAN KUMAR RAM</t>
+    <t>DBS/ 2800/71/24</t>
   </si>
   <si>
-    <t>SANJAY RAM</t>
+    <t>LENZING MIBOM MODI</t>
   </si>
   <si>
-    <t>ANJU DEVI</t>
+    <t>Bolet Modi</t>
   </si>
   <si>
-    <t>09/10/2009</t>
+    <t>Lt. Rebeccah Libang</t>
+  </si>
+  <si>
+    <t>DBS/ 1778/18</t>
+  </si>
+  <si>
+    <t>CHAHAT BEGUM</t>
+  </si>
+  <si>
+    <t>Tasnur Ali Khan</t>
+  </si>
+  <si>
+    <t>Nazma Begum</t>
+  </si>
+  <si>
+    <t>DBS/ 1152/14</t>
+  </si>
+  <si>
+    <t>GAURAV SAHANI</t>
+  </si>
+  <si>
+    <t>Motilal Sahani</t>
+  </si>
+  <si>
+    <t>Rinku Sahani</t>
+  </si>
+  <si>
+    <t>DBS/ 1369/15</t>
+  </si>
+  <si>
+    <t>BIKRANT BISWAKARMA</t>
+  </si>
+  <si>
+    <t>Khadka Biswakarma</t>
+  </si>
+  <si>
+    <t>Rukmini Devi</t>
+  </si>
+  <si>
+    <t>DBS/1357/15</t>
+  </si>
+  <si>
+    <t>ANGUN SAROH</t>
+  </si>
+  <si>
+    <t>taper Saroh</t>
+  </si>
+  <si>
+    <t>Gagam Saroh</t>
+  </si>
+  <si>
+    <t>DBS/ 2608/30/23</t>
+  </si>
+  <si>
+    <t>MUSKAN KUMARI</t>
+  </si>
+  <si>
+    <t>Raju Rai</t>
+  </si>
+  <si>
+    <t>Sumitra Devi</t>
+  </si>
+  <si>
+    <t>DBS/ 2616/38/23</t>
+  </si>
+  <si>
+    <t>KANGKILING Jamoh</t>
+  </si>
+  <si>
+    <t>Kakir Jamoh</t>
+  </si>
+  <si>
+    <t>Oset Jamoh</t>
+  </si>
+  <si>
+    <t>Jenging</t>
+  </si>
+  <si>
+    <t>DBS/ 1759/17</t>
+  </si>
+  <si>
+    <t>RANI SARKAR</t>
+  </si>
+  <si>
+    <t>Bishnu Sarkar</t>
+  </si>
+  <si>
+    <t>Jayanti Sarkar</t>
+  </si>
+  <si>
+    <t>DBS/ 2612/34/23</t>
+  </si>
+  <si>
+    <t>KAYANG MIYU</t>
+  </si>
+  <si>
+    <t>Tai Miyu</t>
+  </si>
+  <si>
+    <t>Ainam Miyu</t>
+  </si>
+  <si>
+    <t>DBS/2605/27/23</t>
+  </si>
+  <si>
+    <t>CHUCHUK TALAR</t>
+  </si>
+  <si>
+    <t>Tapir Talar</t>
+  </si>
+  <si>
+    <t>Yatum Talar</t>
+  </si>
+  <si>
+    <t>Tato</t>
+  </si>
+  <si>
+    <t>DBS/ 1368/15</t>
+  </si>
+  <si>
+    <t>NAVNIT MAHATO</t>
+  </si>
+  <si>
+    <t>Rajen Mahato</t>
+  </si>
+  <si>
+    <t>Anima Mahato</t>
+  </si>
+  <si>
+    <t>DBS/ 2124/20</t>
+  </si>
+  <si>
+    <t>TOBA TASI</t>
+  </si>
+  <si>
+    <t>Mito Tasi</t>
+  </si>
+  <si>
+    <t>Dome Tasi</t>
+  </si>
+  <si>
+    <t>Airgfield</t>
+  </si>
+  <si>
+    <t>DBS/ 2184/21</t>
+  </si>
+  <si>
+    <t>MINAM TALI</t>
+  </si>
+  <si>
+    <t>Regong Tali</t>
+  </si>
+  <si>
+    <t>Openg Yalik Tali</t>
+  </si>
+  <si>
+    <t>DBS/ 1915/18</t>
+  </si>
+  <si>
+    <t>ESHIKA THAPA</t>
+  </si>
+  <si>
+    <t>Motilal Thapa</t>
+  </si>
+  <si>
+    <t>Kumari Thapa</t>
+  </si>
+  <si>
+    <t>DBS/ 1381/15</t>
+  </si>
+  <si>
+    <t>NIMA DORJEE</t>
+  </si>
+  <si>
+    <t>Netam Tashi</t>
+  </si>
+  <si>
+    <t>Anima Tashi</t>
+  </si>
+  <si>
+    <t>DBS/ 1178/14</t>
+  </si>
+  <si>
+    <t>ANUP MAZUMDER</t>
+  </si>
+  <si>
+    <t>Mati Lal Mazumder</t>
+  </si>
+  <si>
+    <t>Supta Mazumder</t>
+  </si>
+  <si>
+    <t>RWD Colony</t>
+  </si>
+  <si>
+    <t>MIBOM TALI</t>
+  </si>
+  <si>
+    <t>Vijay Tali</t>
+  </si>
+  <si>
+    <t>Marpi Tali</t>
+  </si>
+  <si>
+    <t>Mirmir Charali</t>
+  </si>
+  <si>
+    <t>DBS/ 2366/155/22</t>
+  </si>
+  <si>
+    <t>TANONG PANYANG</t>
+  </si>
+  <si>
+    <t>Aje Panyang</t>
+  </si>
+  <si>
+    <t>Tilek Panyang</t>
+  </si>
+  <si>
+    <t>DBS/ 2291/76/22</t>
+  </si>
+  <si>
+    <t>KATEM PERME</t>
+  </si>
+  <si>
+    <t>Zibg Perme</t>
+  </si>
+  <si>
+    <t>Gegul Dai Perme</t>
+  </si>
+  <si>
+    <t>Berung</t>
+  </si>
+  <si>
+    <t>DBS/1941/18</t>
+  </si>
+  <si>
+    <t>GAMPI PADUNG</t>
+  </si>
+  <si>
+    <t>Nagam Padung</t>
+  </si>
+  <si>
+    <t>Gita Padung</t>
+  </si>
+  <si>
+    <t>Nari</t>
+  </si>
+  <si>
+    <t>DBS/ 1396/15</t>
+  </si>
+  <si>
+    <t>SAACHI DEKA</t>
+  </si>
+  <si>
+    <t>Jiten Deka</t>
+  </si>
+  <si>
+    <t>Sikha Deka</t>
+  </si>
+  <si>
+    <t>L/Banskota</t>
+  </si>
+  <si>
+    <t>DBS/ 1252/14</t>
+  </si>
+  <si>
+    <t>SUKMONI NARZARI</t>
+  </si>
+  <si>
+    <t>Ringkhang Narzari</t>
+  </si>
+  <si>
+    <t>Purnima Narzari</t>
+  </si>
+  <si>
+    <t>DBS/ 1155/14</t>
+  </si>
+  <si>
+    <t>ISHAN TAMANG</t>
+  </si>
+  <si>
+    <t>Gore Tamang</t>
+  </si>
+  <si>
+    <t>Maya Tamang</t>
+  </si>
+  <si>
+    <t>DBS/ 2316/104/22</t>
+  </si>
+  <si>
+    <t>VICE TADENG</t>
+  </si>
+  <si>
+    <t>Tabuk Tadeng</t>
+  </si>
+  <si>
+    <t>Yapang Tadeng</t>
+  </si>
+  <si>
+    <t>GTC</t>
+  </si>
+  <si>
+    <t>DBS/ 2280/66/22</t>
+  </si>
+  <si>
+    <t>GANDHI JOMYANG</t>
+  </si>
+  <si>
+    <t>Tamom Jomyang</t>
+  </si>
+  <si>
+    <t>Olak Tamuk</t>
+  </si>
+  <si>
+    <t>DBS/ 2681/03</t>
+  </si>
+  <si>
+    <t>KANGKILING JAMOH</t>
+  </si>
+  <si>
+    <t>kaling Jamoh</t>
+  </si>
+  <si>
+    <t>Marmin Kadu Jamoh</t>
+  </si>
+  <si>
+    <t>APST Colony</t>
+  </si>
+  <si>
+    <t>DBS/ 262/14</t>
+  </si>
+  <si>
+    <t>AISHA KHATUN</t>
+  </si>
+  <si>
+    <t>Sayohar Sheikh</t>
+  </si>
+  <si>
+    <t>Jesmina Begum</t>
+  </si>
+  <si>
+    <t>DBS/2836/106/24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OKI PANYANG </t>
+  </si>
+  <si>
+    <t>ONYOK PANYANG</t>
+  </si>
+  <si>
+    <t>AMANG PANYANG</t>
+  </si>
+  <si>
+    <t>GEKU YINGKIONG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="0_);\(0\)"/>
-    <numFmt numFmtId="179" formatCode="&quot;+91-&quot;#"/>
-    <numFmt numFmtId="180" formatCode="0000\ 0000\ 0000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,32 +748,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -419,8 +773,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -434,26 +796,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -466,33 +821,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -511,8 +843,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -527,9 +875,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -542,7 +918,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,7 +948,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,73 +1062,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,90 +1086,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -752,6 +1128,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -762,30 +1153,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -838,6 +1205,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -851,10 +1242,13 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -863,216 +1257,203 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="29" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="29" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="58" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
-    <cellStyle name="Percent" xfId="6" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
-    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
-    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
-    <cellStyle name="Note" xfId="12" builtinId="10"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="Title" xfId="16" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
-    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
-    <cellStyle name="Input" xfId="21" builtinId="20"/>
-    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
-    <cellStyle name="Good" xfId="23" builtinId="26"/>
-    <cellStyle name="Output" xfId="24" builtinId="21"/>
-    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
-    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bad" xfId="29" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
-    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
-    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
-    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
-    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
-    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -20126,6 +20507,822 @@
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="180975" cy="933450"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rectangle 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8180705" y="190500"/>
+          <a:ext cx="180975" cy="933450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="180975" cy="933450"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rectangle 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8180705" y="190500"/>
+          <a:ext cx="180975" cy="933450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="180975" cy="933450"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rectangle 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8180705" y="190500"/>
+          <a:ext cx="180975" cy="933450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="180975" cy="933450"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8180705" y="190500"/>
+          <a:ext cx="180975" cy="933450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="180975" cy="933450"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectangle 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8180705" y="190500"/>
+          <a:ext cx="180975" cy="933450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="180975" cy="933450"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="147" name="Rectangle 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8180705" y="190500"/>
+          <a:ext cx="180975" cy="933450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr lvl="0" algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
@@ -20417,7 +21614,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R117"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.78095238095238" customWidth="1"/>
@@ -20465,10 +21662,10 @@
       <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
@@ -20487,2444 +21684,1850 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="2:18">
+    <row r="2" customHeight="1" spans="2:18">
       <c r="B2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="7">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="8">
-        <v>8709944868</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="H2" s="5">
+        <v>8974379825</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>20</v>
       </c>
       <c r="J2" s="6"/>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="9">
+        <v>41366</v>
+      </c>
+      <c r="L2" s="9">
+        <v>45397</v>
+      </c>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6">
+        <v>2</v>
+      </c>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="14">
-        <v>41354</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O2" s="7">
-        <v>1108</v>
-      </c>
-      <c r="P2" s="6">
-        <v>2050</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" s="11"/>
+      <c r="R2" s="10"/>
     </row>
     <row r="3" spans="2:18">
       <c r="B3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>1</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="5">
+        <v>8974918088</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="9">
+        <v>40875</v>
+      </c>
+      <c r="L3" s="9">
+        <v>45400</v>
+      </c>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6">
+        <v>2</v>
+      </c>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="8">
-        <v>8051277817</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="14">
-        <v>41358</v>
-      </c>
-      <c r="M3" s="15">
-        <v>931889191872</v>
-      </c>
-      <c r="N3" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O3" s="7">
-        <v>1108</v>
-      </c>
-      <c r="P3" s="6">
-        <v>2050</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" s="11"/>
+      <c r="R3" s="10"/>
     </row>
     <row r="4" spans="2:18">
       <c r="B4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="7">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="8">
-        <v>8676860217</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>32</v>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9162494913</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="J4" s="6"/>
-      <c r="K4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="14">
-        <v>41354</v>
-      </c>
-      <c r="M4" s="15">
-        <v>708735547268</v>
-      </c>
-      <c r="N4" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O4" s="7">
-        <v>1108</v>
-      </c>
-      <c r="P4" s="6">
-        <v>2050</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="R4" s="11"/>
+      <c r="K4" s="9">
+        <v>39726</v>
+      </c>
+      <c r="L4" s="9">
+        <v>45404</v>
+      </c>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6">
+        <v>2</v>
+      </c>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" s="10"/>
     </row>
     <row r="5" spans="2:18">
       <c r="B5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="8">
-        <v>9801294592</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>38</v>
+      <c r="G5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="5">
+        <v>9366054638</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="J5" s="6"/>
-      <c r="K5" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" s="14">
-        <v>41400</v>
-      </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O5" s="7">
-        <v>1108</v>
-      </c>
-      <c r="P5" s="6">
-        <v>2050</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="R5" s="11"/>
+      <c r="K5" s="9">
+        <v>40416</v>
+      </c>
+      <c r="L5" s="9">
+        <v>45412</v>
+      </c>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6">
+        <v>2</v>
+      </c>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="R5" s="10"/>
     </row>
     <row r="6" spans="2:18">
       <c r="B6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
-      <c r="F6" s="7">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="8">
-        <v>8809143325</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>44</v>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="5">
+        <v>8787310869</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="J6" s="6"/>
-      <c r="K6" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L6" s="14">
-        <v>41487</v>
-      </c>
-      <c r="M6" s="15">
-        <v>581426167992</v>
-      </c>
-      <c r="N6" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O6" s="7">
-        <v>1108</v>
-      </c>
-      <c r="P6" s="6">
-        <v>2050</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="R6" s="11"/>
+      <c r="K6" s="9">
+        <v>40725</v>
+      </c>
+      <c r="L6" s="9">
+        <v>45414</v>
+      </c>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6">
+        <v>2</v>
+      </c>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6" s="10"/>
     </row>
     <row r="7" spans="2:18">
       <c r="B7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>48</v>
+        <v>41</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="8">
-        <v>9708845968</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>50</v>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="5">
+        <v>7422968367</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="J7" s="6"/>
-      <c r="K7" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="L7" s="14">
-        <v>41375</v>
-      </c>
-      <c r="M7" s="15">
-        <v>381682220476</v>
-      </c>
-      <c r="N7" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O7" s="7">
-        <v>1105</v>
+      <c r="K7" s="9">
+        <v>40811</v>
+      </c>
+      <c r="L7" s="9">
+        <v>45415</v>
+      </c>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6">
+        <v>2</v>
       </c>
       <c r="P7" s="6"/>
-      <c r="Q7" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="R7" s="11"/>
+      <c r="Q7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R7" s="10"/>
     </row>
     <row r="8" spans="2:18">
       <c r="B8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>1</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="8">
-        <v>9934954656</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>56</v>
+      <c r="G8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="5">
+        <v>9862544440</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="J8" s="6"/>
-      <c r="K8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="L8" s="14">
-        <v>41827</v>
-      </c>
-      <c r="M8" s="15"/>
-      <c r="N8" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O8" s="7">
-        <v>1105</v>
+      <c r="K8" s="9">
+        <v>40774</v>
+      </c>
+      <c r="L8" s="9">
+        <v>45415</v>
+      </c>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6">
+        <v>2</v>
       </c>
       <c r="P8" s="6"/>
-      <c r="Q8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="R8" s="11"/>
+      <c r="Q8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="R8" s="10"/>
     </row>
     <row r="9" spans="2:18">
       <c r="B9" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="8">
-        <v>9661903634</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>32</v>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="5">
+        <v>9366995633</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="J9" s="6"/>
-      <c r="K9" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="L9" s="14">
-        <v>42115</v>
-      </c>
-      <c r="M9" s="15"/>
-      <c r="N9" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O9" s="7">
-        <v>1108</v>
+      <c r="K9" s="9">
+        <v>38917</v>
+      </c>
+      <c r="L9" s="9">
+        <v>45422</v>
+      </c>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6">
+        <v>2</v>
       </c>
       <c r="P9" s="6"/>
-      <c r="Q9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="R9" s="11"/>
+      <c r="Q9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="R9" s="10"/>
     </row>
     <row r="10" spans="2:18">
       <c r="B10" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>65</v>
+        <v>55</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <v>1</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="8">
-        <v>9631217257</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>56</v>
+      <c r="G10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="5">
+        <v>9862050726</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="J10" s="6"/>
-      <c r="K10" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="L10" s="14">
-        <v>41481</v>
-      </c>
-      <c r="M10" s="15">
-        <v>303998497368</v>
-      </c>
-      <c r="N10" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O10" s="7">
-        <v>1108</v>
+      <c r="K10" s="9">
+        <v>40743</v>
+      </c>
+      <c r="L10" s="9">
+        <v>45425</v>
+      </c>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6">
+        <v>2</v>
       </c>
       <c r="P10" s="6"/>
-      <c r="Q10" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="R10" s="11"/>
+      <c r="Q10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R10" s="10"/>
     </row>
     <row r="11" spans="2:18">
       <c r="B11" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>69</v>
+        <v>59</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
-      <c r="F11" s="7">
+      <c r="F11" s="5">
         <v>1</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="8">
-        <v>9661903634</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>71</v>
+      <c r="G11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="5">
+        <v>7005686284</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="J11" s="6"/>
-      <c r="K11" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="14">
-        <v>41741</v>
-      </c>
-      <c r="M11" s="15"/>
-      <c r="N11" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O11" s="7">
-        <v>1108</v>
+      <c r="K11" s="9">
+        <v>40178</v>
+      </c>
+      <c r="L11" s="9">
+        <v>45425</v>
+      </c>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6">
+        <v>2</v>
       </c>
       <c r="P11" s="6"/>
-      <c r="Q11" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="R11" s="11"/>
+      <c r="Q11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R11" s="10"/>
     </row>
     <row r="12" spans="2:18">
       <c r="B12" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>74</v>
+        <v>63</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <v>1</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="H12" s="8">
-        <v>9709536582</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>76</v>
+      <c r="G12" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="5">
+        <v>6009070933</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="J12" s="6"/>
-      <c r="K12" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="L12" s="14">
-        <v>41390</v>
-      </c>
-      <c r="M12" s="15">
-        <v>407076065807</v>
-      </c>
-      <c r="N12" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O12" s="7">
-        <v>1108</v>
+      <c r="K12" s="9">
+        <v>40270</v>
+      </c>
+      <c r="L12" s="9">
+        <v>45426</v>
+      </c>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6">
+        <v>2</v>
       </c>
       <c r="P12" s="6"/>
-      <c r="Q12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="R12" s="11"/>
+      <c r="Q12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R12" s="10"/>
     </row>
     <row r="13" spans="2:18">
       <c r="B13" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>80</v>
+        <v>67</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <v>0</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="H13" s="8">
-        <v>9801294592</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>38</v>
+      <c r="G13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="5">
+        <v>7005175311</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="J13" s="6"/>
-      <c r="K13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L13" s="14">
-        <v>41400</v>
-      </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O13" s="7">
-        <v>1108</v>
+      <c r="K13" s="9">
+        <v>40521</v>
+      </c>
+      <c r="L13" s="9">
+        <v>45426</v>
+      </c>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6">
+        <v>2</v>
       </c>
       <c r="P13" s="6"/>
-      <c r="Q13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="R13" s="11"/>
+      <c r="Q13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R13" s="10"/>
     </row>
     <row r="14" spans="2:18">
       <c r="B14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>83</v>
+        <v>71</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="7">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" s="8">
-        <v>8051814705</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>85</v>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" s="5">
+        <v>7628937591</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="J14" s="6"/>
-      <c r="K14" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="L14" s="14">
-        <v>41975</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="N14" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O14" s="7">
-        <v>1108</v>
+      <c r="K14" s="9">
+        <v>41054</v>
+      </c>
+      <c r="L14" s="9">
+        <v>45426</v>
+      </c>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6">
+        <v>2</v>
       </c>
       <c r="P14" s="6"/>
-      <c r="Q14" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="R14" s="11"/>
+      <c r="Q14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" spans="2:18">
       <c r="B15" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>90</v>
+        <v>76</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="7">
+      <c r="F15" s="5">
         <v>0</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H15" s="8">
-        <v>9709329175</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>92</v>
+      <c r="G15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="5">
+        <v>7085808992</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="J15" s="6"/>
-      <c r="K15" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="L15" s="14">
-        <v>43214</v>
-      </c>
-      <c r="M15" s="15"/>
-      <c r="N15" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O15" s="7">
-        <v>1108</v>
+      <c r="K15" s="9">
+        <v>40592</v>
+      </c>
+      <c r="L15" s="9">
+        <v>45427</v>
+      </c>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6">
+        <v>2</v>
       </c>
       <c r="P15" s="6"/>
-      <c r="Q15" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="R15" s="11"/>
+      <c r="Q15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="R15" s="10"/>
     </row>
     <row r="16" spans="2:18">
-      <c r="B16" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>96</v>
+      <c r="B16" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
-      <c r="F16" s="7">
+      <c r="F16" s="5">
         <v>1</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H16" s="8">
-        <v>9955552903</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>76</v>
+      <c r="G16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="5">
+        <v>7628976205</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="J16" s="6"/>
-      <c r="K16" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="L16" s="14">
-        <v>41473</v>
-      </c>
-      <c r="M16" s="15">
-        <v>201443844348</v>
-      </c>
-      <c r="N16" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O16" s="7">
-        <v>1106</v>
+      <c r="K16" s="9">
+        <v>40873</v>
+      </c>
+      <c r="L16" s="9">
+        <v>45429</v>
+      </c>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6">
+        <v>2</v>
       </c>
       <c r="P16" s="6"/>
-      <c r="Q16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="R16" s="11"/>
+      <c r="Q16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="R16" s="10"/>
     </row>
     <row r="17" spans="2:18">
-      <c r="B17" s="5"/>
-      <c r="C17" s="6" t="s">
-        <v>99</v>
+      <c r="B17" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="7">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="6" t="s">
-        <v>101</v>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="5">
+        <v>9578057414</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="J17" s="6"/>
-      <c r="K17" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="L17" s="14"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="7">
-        <v>1064</v>
-      </c>
-      <c r="O17" s="7"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="9">
+        <v>45432</v>
+      </c>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6">
+        <v>2</v>
+      </c>
       <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="11"/>
+      <c r="Q17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="R17" s="10"/>
     </row>
     <row r="18" spans="2:18">
-      <c r="B18" s="5"/>
-      <c r="C18" s="6" t="s">
-        <v>103</v>
+      <c r="B18" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="7">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="6" t="s">
-        <v>105</v>
+      <c r="F18" s="5">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" s="5">
+        <v>7085567125</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="J18" s="6"/>
-      <c r="K18" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="L18" s="14"/>
-      <c r="M18" s="15"/>
+      <c r="K18" s="9">
+        <v>40826</v>
+      </c>
+      <c r="L18" s="9">
+        <v>45432</v>
+      </c>
+      <c r="M18" s="6"/>
       <c r="N18" s="6"/>
-      <c r="O18" s="7"/>
+      <c r="O18" s="6">
+        <v>2</v>
+      </c>
       <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="11"/>
+      <c r="Q18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="R18" s="10"/>
     </row>
     <row r="19" spans="2:18">
-      <c r="B19" s="5"/>
-      <c r="C19" s="6" t="s">
-        <v>107</v>
+      <c r="B19" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="7">
+      <c r="F19" s="5">
         <v>0</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="6" t="s">
-        <v>109</v>
+      <c r="G19" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" s="5">
+        <v>7005343014</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="J19" s="6"/>
-      <c r="K19" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="L19" s="14"/>
-      <c r="M19" s="15"/>
+      <c r="K19" s="9">
+        <v>41255</v>
+      </c>
+      <c r="L19" s="9">
+        <v>45434</v>
+      </c>
+      <c r="M19" s="6"/>
       <c r="N19" s="6"/>
-      <c r="O19" s="7"/>
+      <c r="O19" s="6">
+        <v>2</v>
+      </c>
       <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="11"/>
+      <c r="Q19" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R19" s="10"/>
     </row>
     <row r="20" spans="2:18">
-      <c r="B20" s="5"/>
-      <c r="C20" s="6"/>
+      <c r="B20" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>100</v>
+      </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
+      <c r="F20" s="5">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" s="5">
+        <v>7005917179</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J20" s="6"/>
+      <c r="K20" s="9">
+        <v>40657</v>
+      </c>
+      <c r="L20" s="9">
+        <v>45436</v>
+      </c>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6">
+        <v>2</v>
+      </c>
       <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="11"/>
+      <c r="Q20" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="R20" s="10"/>
     </row>
     <row r="21" spans="2:18">
-      <c r="B21" s="5"/>
-      <c r="C21" s="6"/>
+      <c r="B21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>104</v>
+      </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" s="5">
+        <v>6009200486</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="J21" s="6"/>
+      <c r="K21" s="9">
+        <v>40445</v>
+      </c>
+      <c r="L21" s="9">
+        <v>45436</v>
+      </c>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6">
+        <v>2</v>
+      </c>
       <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="11"/>
+      <c r="Q21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="R21" s="10"/>
     </row>
     <row r="22" spans="2:18">
-      <c r="B22" s="5"/>
-      <c r="C22" s="6"/>
+      <c r="B22" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
+      <c r="F22" s="5">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H22" s="5">
+        <v>8787569385</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J22" s="6"/>
+      <c r="K22" s="9">
+        <v>40814</v>
+      </c>
+      <c r="L22" s="9">
+        <v>45436</v>
+      </c>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6">
+        <v>2</v>
+      </c>
       <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="11"/>
+      <c r="Q22" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="R22" s="10"/>
     </row>
     <row r="23" spans="2:18">
-      <c r="B23" s="5"/>
-      <c r="C23" s="6"/>
+      <c r="B23" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" s="5">
+        <v>9862501903</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J23" s="6"/>
+      <c r="K23" s="9">
+        <v>40416</v>
+      </c>
+      <c r="L23" s="9">
+        <v>45437</v>
+      </c>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6">
+        <v>2</v>
+      </c>
       <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="11"/>
+      <c r="Q23" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R23" s="10"/>
     </row>
     <row r="24" spans="2:18">
-      <c r="B24" s="5"/>
-      <c r="C24" s="6"/>
+      <c r="B24" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>116</v>
+      </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="15"/>
+      <c r="F24" s="5">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H24" s="5">
+        <v>7005547609</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J24" s="6"/>
+      <c r="K24" s="9">
+        <v>40175</v>
+      </c>
+      <c r="L24" s="9">
+        <v>45439</v>
+      </c>
+      <c r="M24" s="6"/>
       <c r="N24" s="6"/>
-      <c r="O24" s="7"/>
+      <c r="O24" s="6">
+        <v>2</v>
+      </c>
       <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="11"/>
+      <c r="Q24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="R24" s="10"/>
     </row>
     <row r="25" spans="2:18">
-      <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
+      <c r="B25" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>120</v>
+      </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="15"/>
+      <c r="F25" s="5">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H25" s="5">
+        <v>8837303003</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="J25" s="6"/>
+      <c r="K25" s="9">
+        <v>41216</v>
+      </c>
+      <c r="L25" s="9">
+        <v>45439</v>
+      </c>
+      <c r="M25" s="6"/>
       <c r="N25" s="6"/>
-      <c r="O25" s="7"/>
+      <c r="O25" s="6">
+        <v>2</v>
+      </c>
       <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="11"/>
+      <c r="Q25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="R25" s="10"/>
     </row>
     <row r="26" spans="2:18">
-      <c r="B26" s="5"/>
-      <c r="C26" s="6"/>
+      <c r="B26" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>124</v>
+      </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="15"/>
+      <c r="F26" s="5">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H26" s="5">
+        <v>7005529793</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J26" s="6"/>
+      <c r="K26" s="9">
+        <v>40681</v>
+      </c>
+      <c r="L26" s="9">
+        <v>45439</v>
+      </c>
+      <c r="M26" s="6"/>
       <c r="N26" s="6"/>
-      <c r="O26" s="7"/>
+      <c r="O26" s="6">
+        <v>2</v>
+      </c>
       <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="11"/>
+      <c r="Q26" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="R26" s="10"/>
     </row>
-    <row r="27" spans="2:18">
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
+    <row r="27" spans="2:17">
+      <c r="B27" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
+      <c r="F27" s="5">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" s="5">
+        <v>7630869411</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J27" s="6"/>
+      <c r="K27" s="9">
+        <v>39906</v>
+      </c>
+      <c r="L27" s="9">
+        <v>45439</v>
+      </c>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6">
+        <v>2</v>
+      </c>
       <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="11"/>
+      <c r="Q27" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="28" spans="2:18">
-      <c r="B28" s="5"/>
-      <c r="C28" s="6"/>
+    <row r="28" spans="2:17">
+      <c r="B28" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
+      <c r="F28" s="5">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H28" s="5">
+        <v>9774758348</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J28" s="6"/>
+      <c r="K28" s="9">
+        <v>40760</v>
+      </c>
+      <c r="L28" s="9">
+        <v>45439</v>
+      </c>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6">
+        <v>2</v>
+      </c>
       <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="11"/>
+      <c r="Q28" s="5" t="s">
+        <v>135</v>
+      </c>
     </row>
-    <row r="29" spans="2:18">
-      <c r="B29" s="5"/>
-      <c r="C29" s="6"/>
+    <row r="29" spans="2:17">
+      <c r="B29" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>137</v>
+      </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
+      <c r="F29" s="5">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H29" s="5">
+        <v>9615754799</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J29" s="6"/>
+      <c r="K29" s="9">
+        <v>40271</v>
+      </c>
+      <c r="L29" s="9">
+        <v>45439</v>
+      </c>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6">
+        <v>2</v>
+      </c>
       <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="11"/>
+      <c r="Q29" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="30" spans="2:18">
-      <c r="B30" s="5"/>
-      <c r="C30" s="6"/>
+    <row r="30" spans="2:17">
+      <c r="B30" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
+      <c r="F30" s="5">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="H30" s="5">
+        <v>8011554173</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="J30" s="6"/>
+      <c r="K30" s="9">
+        <v>40744</v>
+      </c>
+      <c r="L30" s="9">
+        <v>45439</v>
+      </c>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6">
+        <v>2</v>
+      </c>
       <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="11"/>
+      <c r="Q30" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="31" spans="2:18">
-      <c r="B31" s="5"/>
-      <c r="C31" s="6"/>
+    <row r="31" spans="2:17">
+      <c r="B31" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>145</v>
+      </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="15"/>
+      <c r="F31" s="5">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H31" s="5">
+        <v>8413828468</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="J31" s="6"/>
+      <c r="K31" s="9">
+        <v>40733</v>
+      </c>
+      <c r="L31" s="9">
+        <v>45439</v>
+      </c>
+      <c r="M31" s="6"/>
       <c r="N31" s="6"/>
-      <c r="O31" s="7"/>
+      <c r="O31" s="6">
+        <v>2</v>
+      </c>
       <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="11"/>
+      <c r="Q31" s="5" t="s">
+        <v>148</v>
+      </c>
     </row>
-    <row r="32" spans="2:18">
-      <c r="B32" s="5"/>
-      <c r="C32" s="6"/>
+    <row r="32" spans="2:17">
+      <c r="B32" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>150</v>
+      </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="15"/>
+      <c r="F32" s="5">
+        <v>1</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="H32" s="5">
+        <v>8132809210</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="J32" s="6"/>
+      <c r="K32" s="9">
+        <v>40654</v>
+      </c>
+      <c r="L32" s="9">
+        <v>45441</v>
+      </c>
+      <c r="M32" s="6"/>
       <c r="N32" s="6"/>
-      <c r="O32" s="7"/>
+      <c r="O32" s="6">
+        <v>2</v>
+      </c>
       <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="11"/>
+      <c r="Q32" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="33" spans="2:18">
-      <c r="B33" s="5"/>
-      <c r="C33" s="6"/>
+    <row r="33" spans="2:17">
+      <c r="B33" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>154</v>
+      </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="15"/>
+      <c r="F33" s="5">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H33" s="5">
+        <v>6003438913</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J33" s="6"/>
+      <c r="K33" s="9">
+        <v>41366</v>
+      </c>
+      <c r="L33" s="9">
+        <v>45441</v>
+      </c>
+      <c r="M33" s="6"/>
       <c r="N33" s="6"/>
-      <c r="O33" s="7"/>
+      <c r="O33" s="6">
+        <v>2</v>
+      </c>
       <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="11"/>
+      <c r="Q33" s="5" t="s">
+        <v>157</v>
+      </c>
     </row>
-    <row r="34" spans="2:18">
-      <c r="B34" s="5"/>
-      <c r="C34" s="6"/>
+    <row r="34" spans="2:17">
+      <c r="B34" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="15"/>
+      <c r="F34" s="5">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H34" s="5">
+        <v>7085952715</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="J34" s="6"/>
+      <c r="K34" s="9">
+        <v>41538</v>
+      </c>
+      <c r="L34" s="9">
+        <v>45442</v>
+      </c>
+      <c r="M34" s="6"/>
       <c r="N34" s="6"/>
-      <c r="O34" s="7"/>
+      <c r="O34" s="6">
+        <v>2</v>
+      </c>
       <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="11"/>
+      <c r="Q34" s="5"/>
     </row>
-    <row r="35" spans="2:18">
-      <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
+    <row r="35" spans="2:17">
+      <c r="B35" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>163</v>
+      </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="15"/>
+      <c r="F35" s="5">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H35" s="5">
+        <v>8119930346</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="J35" s="6"/>
+      <c r="K35" s="9">
+        <v>40699</v>
+      </c>
+      <c r="L35" s="9">
+        <v>45442</v>
+      </c>
+      <c r="M35" s="6"/>
       <c r="N35" s="6"/>
-      <c r="O35" s="7"/>
+      <c r="O35" s="6">
+        <v>2</v>
+      </c>
       <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="11"/>
+      <c r="Q35" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="36" spans="2:17">
-      <c r="B36" s="5"/>
-      <c r="C36" s="6"/>
+      <c r="B36" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
+      <c r="F36" s="5">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H36" s="5">
+        <v>8257072756</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="J36" s="6"/>
+      <c r="K36" s="9">
+        <v>40307</v>
+      </c>
+      <c r="L36" s="9">
+        <v>45442</v>
+      </c>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6">
+        <v>2</v>
+      </c>
       <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
+      <c r="Q36" s="5" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="37" spans="2:17">
-      <c r="B37" s="10"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="16"/>
-      <c r="Q37" s="11"/>
+      <c r="B37" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="5">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H37" s="5">
+        <v>7005627797</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="J37" s="6"/>
+      <c r="K37" s="9">
+        <v>40765</v>
+      </c>
+      <c r="L37" s="9">
+        <v>45443</v>
+      </c>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6">
+        <v>2</v>
+      </c>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="5" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="38" spans="2:17">
-      <c r="B38" s="10"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="11"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="11"/>
+      <c r="B38" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="5">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H38" s="5">
+        <v>8132816132</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J38" s="6"/>
+      <c r="K38" s="9">
+        <v>40432</v>
+      </c>
+      <c r="L38" s="9">
+        <v>45446</v>
+      </c>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6">
+        <v>2</v>
+      </c>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="5" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="39" spans="2:17">
-      <c r="B39" s="10"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="11"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="11"/>
+      <c r="B39" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="5">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H39" s="5">
+        <v>7085720477</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="J39" s="6"/>
+      <c r="K39" s="9">
+        <v>41716</v>
+      </c>
+      <c r="L39" s="9">
+        <v>45446</v>
+      </c>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6">
+        <v>2</v>
+      </c>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="5" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="40" spans="2:17">
-      <c r="B40" s="10"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="11"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="11"/>
+      <c r="B40" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="5">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="H40" s="5">
+        <v>9436639889</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J40" s="6"/>
+      <c r="K40" s="9">
+        <v>40448</v>
+      </c>
+      <c r="L40" s="9">
+        <v>40448</v>
+      </c>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6">
+        <v>2</v>
+      </c>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="5" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="41" spans="2:17">
-      <c r="B41" s="10"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="16"/>
-      <c r="Q41" s="11"/>
+      <c r="B41" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="5">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="H41" s="5">
+        <v>9402034086</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="J41" s="6"/>
+      <c r="K41" s="9">
+        <v>41246</v>
+      </c>
+      <c r="L41" s="9">
+        <v>45446</v>
+      </c>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6">
+        <v>2</v>
+      </c>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="5" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="42" spans="2:17">
-      <c r="B42" s="10"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="11"/>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="11"/>
+      <c r="B42" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="5">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H42" s="5">
+        <v>8974616250</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J42" s="6"/>
+      <c r="K42" s="9">
+        <v>41226</v>
+      </c>
+      <c r="L42" s="9">
+        <v>41226</v>
+      </c>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6">
+        <v>2</v>
+      </c>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="5" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="43" spans="2:17">
-      <c r="B43" s="10"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="16"/>
-      <c r="Q43" s="11"/>
+      <c r="B43" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="5">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="H43" s="5">
+        <v>7085225075</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="J43" s="6"/>
+      <c r="K43" s="9">
+        <v>40648</v>
+      </c>
+      <c r="L43" s="9">
+        <v>45448</v>
+      </c>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6">
+        <v>2</v>
+      </c>
+      <c r="P43" s="6"/>
+      <c r="Q43" s="5" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="44" spans="2:17">
-      <c r="B44" s="10"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="16"/>
-      <c r="Q44" s="11"/>
+      <c r="B44" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="5">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H44" s="5">
+        <v>8974549309</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="J44" s="6"/>
+      <c r="K44" s="9">
+        <v>39830</v>
+      </c>
+      <c r="L44" s="9">
+        <v>45448</v>
+      </c>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6">
+        <v>2</v>
+      </c>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="45" spans="3:17">
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="16"/>
-      <c r="Q45" s="11"/>
+    <row r="45" spans="2:17">
+      <c r="B45" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="5">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="H45" s="5">
+        <v>6009344265</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="J45" s="6"/>
+      <c r="K45" s="9">
+        <v>41143</v>
+      </c>
+      <c r="L45" s="9">
+        <v>45448</v>
+      </c>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6">
+        <v>2</v>
+      </c>
+      <c r="P45" s="6"/>
+      <c r="Q45" s="5" t="s">
+        <v>210</v>
+      </c>
     </row>
-    <row r="46" spans="3:17">
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="16"/>
-      <c r="Q46" s="11"/>
+    <row r="46" spans="2:17">
+      <c r="B46" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="5">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="H46" s="5">
+        <v>7627992951</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="J46" s="6"/>
+      <c r="K46" s="9">
+        <v>40392</v>
+      </c>
+      <c r="L46" s="9">
+        <v>45449</v>
+      </c>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6">
+        <v>2</v>
+      </c>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="5" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="47" spans="3:17">
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="12"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="11"/>
-      <c r="P47" s="16"/>
-      <c r="Q47" s="11"/>
+    <row r="47" spans="2:17">
+      <c r="B47" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="5">
+        <v>0</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H47" s="5">
+        <v>8798517907</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="J47" s="6"/>
+      <c r="K47" s="9">
+        <v>40821</v>
+      </c>
+      <c r="L47" s="9">
+        <v>45454</v>
+      </c>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6">
+        <v>2</v>
+      </c>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="5" t="s">
+        <v>219</v>
+      </c>
     </row>
-    <row r="48" spans="3:17">
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
-      <c r="O48" s="11"/>
-      <c r="P48" s="16"/>
-      <c r="Q48" s="11"/>
+    <row r="48" spans="2:17">
+      <c r="B48" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="5">
+        <v>1</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H48" s="5">
+        <v>7005825139</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="J48" s="6"/>
+      <c r="K48" s="9">
+        <v>39958</v>
+      </c>
+      <c r="L48" s="9">
+        <v>45458</v>
+      </c>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6">
+        <v>2</v>
+      </c>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="49" spans="3:17">
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="12"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="11"/>
-      <c r="O49" s="11"/>
-      <c r="P49" s="16"/>
-      <c r="Q49" s="11"/>
-    </row>
-    <row r="50" spans="3:17">
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="11"/>
-      <c r="P50" s="16"/>
-      <c r="Q50" s="11"/>
-    </row>
-    <row r="51" spans="3:17">
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="16"/>
-      <c r="Q51" s="11"/>
-    </row>
-    <row r="52" spans="3:17">
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="16"/>
-      <c r="Q52" s="11"/>
-    </row>
-    <row r="53" spans="3:17">
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="12"/>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="11"/>
-      <c r="P53" s="16"/>
-      <c r="Q53" s="11"/>
-    </row>
-    <row r="54" spans="3:17">
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11"/>
-      <c r="O54" s="11"/>
-      <c r="P54" s="16"/>
-      <c r="Q54" s="11"/>
-    </row>
-    <row r="55" spans="3:17">
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="11"/>
-      <c r="J55" s="12"/>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="11"/>
-      <c r="O55" s="11"/>
-      <c r="P55" s="16"/>
-      <c r="Q55" s="11"/>
-    </row>
-    <row r="56" spans="3:17">
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="11"/>
-      <c r="P56" s="16"/>
-      <c r="Q56" s="11"/>
-    </row>
-    <row r="57" spans="3:17">
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="11"/>
-      <c r="O57" s="11"/>
-      <c r="P57" s="16"/>
-      <c r="Q57" s="11"/>
-    </row>
-    <row r="58" spans="3:17">
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="12"/>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="11"/>
-      <c r="O58" s="11"/>
-      <c r="P58" s="16"/>
-      <c r="Q58" s="11"/>
-    </row>
-    <row r="59" spans="3:17">
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="12"/>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="11"/>
-      <c r="O59" s="11"/>
-      <c r="P59" s="16"/>
-      <c r="Q59" s="11"/>
-    </row>
-    <row r="60" spans="3:17">
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="11"/>
-      <c r="J60" s="12"/>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="11"/>
-      <c r="N60" s="11"/>
-      <c r="O60" s="11"/>
-      <c r="P60" s="16"/>
-      <c r="Q60" s="11"/>
-    </row>
-    <row r="61" spans="3:17">
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="12"/>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="11"/>
-      <c r="O61" s="11"/>
-      <c r="P61" s="16"/>
-      <c r="Q61" s="11"/>
-    </row>
-    <row r="62" spans="3:17">
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="12"/>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="11"/>
-      <c r="O62" s="11"/>
-      <c r="P62" s="16"/>
-      <c r="Q62" s="11"/>
-    </row>
-    <row r="63" spans="3:17">
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="12"/>
-      <c r="I63" s="11"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="11"/>
-      <c r="O63" s="11"/>
-      <c r="P63" s="16"/>
-      <c r="Q63" s="11"/>
-    </row>
-    <row r="64" spans="3:17">
-      <c r="C64" s="11"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="12"/>
-      <c r="I64" s="11"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="11"/>
-      <c r="O64" s="11"/>
-      <c r="P64" s="16"/>
-      <c r="Q64" s="11"/>
-    </row>
-    <row r="65" spans="3:17">
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="12"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="11"/>
-      <c r="O65" s="11"/>
-      <c r="P65" s="16"/>
-      <c r="Q65" s="11"/>
-    </row>
-    <row r="66" spans="3:17">
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="12"/>
-      <c r="I66" s="11"/>
-      <c r="J66" s="12"/>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="11"/>
-      <c r="O66" s="11"/>
-      <c r="P66" s="16"/>
-      <c r="Q66" s="11"/>
-    </row>
-    <row r="67" spans="3:17">
-      <c r="C67" s="11"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="12"/>
-      <c r="I67" s="11"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="11"/>
-      <c r="O67" s="11"/>
-      <c r="P67" s="16"/>
-      <c r="Q67" s="11"/>
-    </row>
-    <row r="68" spans="3:17">
-      <c r="C68" s="11"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="12"/>
-      <c r="I68" s="11"/>
-      <c r="J68" s="12"/>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="11"/>
-      <c r="O68" s="11"/>
-      <c r="P68" s="16"/>
-      <c r="Q68" s="11"/>
-    </row>
-    <row r="69" spans="3:17">
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="12"/>
-      <c r="I69" s="11"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="11"/>
-      <c r="O69" s="11"/>
-      <c r="P69" s="16"/>
-      <c r="Q69" s="11"/>
-    </row>
-    <row r="70" spans="3:17">
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="12"/>
-      <c r="I70" s="11"/>
-      <c r="J70" s="12"/>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="11"/>
-      <c r="O70" s="11"/>
-      <c r="P70" s="16"/>
-      <c r="Q70" s="11"/>
-    </row>
-    <row r="71" spans="3:17">
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="12"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="12"/>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="11"/>
-      <c r="O71" s="11"/>
-      <c r="P71" s="16"/>
-      <c r="Q71" s="11"/>
-    </row>
-    <row r="72" spans="3:17">
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="12"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="12"/>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="11"/>
-      <c r="O72" s="11"/>
-      <c r="P72" s="16"/>
-      <c r="Q72" s="11"/>
-    </row>
-    <row r="73" spans="3:17">
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="12"/>
-      <c r="I73" s="11"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="11"/>
-      <c r="O73" s="11"/>
-      <c r="P73" s="16"/>
-      <c r="Q73" s="11"/>
-    </row>
-    <row r="74" spans="3:17">
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="12"/>
-      <c r="I74" s="11"/>
-      <c r="J74" s="12"/>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="11"/>
-      <c r="O74" s="11"/>
-      <c r="P74" s="16"/>
-      <c r="Q74" s="11"/>
-    </row>
-    <row r="75" spans="3:17">
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="12"/>
-      <c r="I75" s="11"/>
-      <c r="J75" s="12"/>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="11"/>
-      <c r="O75" s="11"/>
-      <c r="P75" s="16"/>
-      <c r="Q75" s="11"/>
-    </row>
-    <row r="76" spans="3:17">
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="12"/>
-      <c r="I76" s="11"/>
-      <c r="J76" s="12"/>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="11"/>
-      <c r="O76" s="11"/>
-      <c r="P76" s="16"/>
-      <c r="Q76" s="11"/>
-    </row>
-    <row r="77" spans="3:17">
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11"/>
-      <c r="H77" s="12"/>
-      <c r="I77" s="11"/>
-      <c r="J77" s="12"/>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="11"/>
-      <c r="N77" s="11"/>
-      <c r="O77" s="11"/>
-      <c r="P77" s="16"/>
-      <c r="Q77" s="11"/>
-    </row>
-    <row r="78" spans="3:17">
-      <c r="C78" s="11"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="12"/>
-      <c r="I78" s="11"/>
-      <c r="J78" s="12"/>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="11"/>
-      <c r="O78" s="11"/>
-      <c r="P78" s="16"/>
-      <c r="Q78" s="11"/>
-    </row>
-    <row r="79" spans="3:17">
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="12"/>
-      <c r="I79" s="11"/>
-      <c r="J79" s="12"/>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="11"/>
-      <c r="O79" s="11"/>
-      <c r="P79" s="16"/>
-      <c r="Q79" s="11"/>
-    </row>
-    <row r="80" spans="3:17">
-      <c r="C80" s="11"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="12"/>
-      <c r="I80" s="11"/>
-      <c r="J80" s="12"/>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="11"/>
-      <c r="N80" s="11"/>
-      <c r="O80" s="11"/>
-      <c r="P80" s="16"/>
-      <c r="Q80" s="11"/>
-    </row>
-    <row r="81" spans="3:17">
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="12"/>
-      <c r="I81" s="11"/>
-      <c r="J81" s="12"/>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="11"/>
-      <c r="N81" s="11"/>
-      <c r="O81" s="11"/>
-      <c r="P81" s="16"/>
-      <c r="Q81" s="11"/>
-    </row>
-    <row r="82" spans="3:17">
-      <c r="C82" s="11"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
-      <c r="G82" s="11"/>
-      <c r="H82" s="12"/>
-      <c r="I82" s="11"/>
-      <c r="J82" s="12"/>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="11"/>
-      <c r="N82" s="11"/>
-      <c r="O82" s="11"/>
-      <c r="P82" s="16"/>
-      <c r="Q82" s="11"/>
-    </row>
-    <row r="83" spans="3:17">
-      <c r="C83" s="11"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="11"/>
-      <c r="H83" s="12"/>
-      <c r="I83" s="11"/>
-      <c r="J83" s="12"/>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="11"/>
-      <c r="N83" s="11"/>
-      <c r="O83" s="11"/>
-      <c r="P83" s="16"/>
-      <c r="Q83" s="11"/>
-    </row>
-    <row r="84" spans="3:17">
-      <c r="C84" s="11"/>
-      <c r="D84" s="11"/>
-      <c r="E84" s="11"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="11"/>
-      <c r="H84" s="12"/>
-      <c r="I84" s="11"/>
-      <c r="J84" s="12"/>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="11"/>
-      <c r="N84" s="11"/>
-      <c r="O84" s="11"/>
-      <c r="P84" s="16"/>
-      <c r="Q84" s="11"/>
-    </row>
-    <row r="85" spans="3:17">
-      <c r="C85" s="11"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="12"/>
-      <c r="I85" s="11"/>
-      <c r="J85" s="12"/>
-      <c r="K85" s="16"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="11"/>
-      <c r="N85" s="11"/>
-      <c r="O85" s="11"/>
-      <c r="P85" s="16"/>
-      <c r="Q85" s="11"/>
-    </row>
-    <row r="86" spans="3:17">
-      <c r="C86" s="11"/>
-      <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11"/>
-      <c r="H86" s="12"/>
-      <c r="I86" s="11"/>
-      <c r="J86" s="12"/>
-      <c r="K86" s="16"/>
-      <c r="L86" s="16"/>
-      <c r="M86" s="11"/>
-      <c r="N86" s="11"/>
-      <c r="O86" s="11"/>
-      <c r="P86" s="16"/>
-      <c r="Q86" s="11"/>
-    </row>
-    <row r="87" spans="3:17">
-      <c r="C87" s="11"/>
-      <c r="D87" s="11"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="11"/>
-      <c r="H87" s="12"/>
-      <c r="I87" s="11"/>
-      <c r="J87" s="12"/>
-      <c r="K87" s="16"/>
-      <c r="L87" s="16"/>
-      <c r="M87" s="11"/>
-      <c r="N87" s="11"/>
-      <c r="O87" s="11"/>
-      <c r="P87" s="16"/>
-      <c r="Q87" s="11"/>
-    </row>
-    <row r="88" spans="3:17">
-      <c r="C88" s="11"/>
-      <c r="D88" s="11"/>
-      <c r="E88" s="11"/>
-      <c r="F88" s="11"/>
-      <c r="G88" s="11"/>
-      <c r="H88" s="12"/>
-      <c r="I88" s="11"/>
-      <c r="J88" s="12"/>
-      <c r="K88" s="16"/>
-      <c r="L88" s="16"/>
-      <c r="M88" s="11"/>
-      <c r="N88" s="11"/>
-      <c r="O88" s="11"/>
-      <c r="P88" s="16"/>
-      <c r="Q88" s="11"/>
-    </row>
-    <row r="89" spans="3:17">
-      <c r="C89" s="11"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
-      <c r="G89" s="11"/>
-      <c r="H89" s="12"/>
-      <c r="I89" s="11"/>
-      <c r="J89" s="12"/>
-      <c r="K89" s="16"/>
-      <c r="L89" s="16"/>
-      <c r="M89" s="11"/>
-      <c r="N89" s="11"/>
-      <c r="O89" s="11"/>
-      <c r="P89" s="16"/>
-      <c r="Q89" s="11"/>
-    </row>
-    <row r="90" spans="3:17">
-      <c r="C90" s="11"/>
-      <c r="D90" s="11"/>
-      <c r="E90" s="11"/>
-      <c r="F90" s="11"/>
-      <c r="G90" s="11"/>
-      <c r="H90" s="12"/>
-      <c r="I90" s="11"/>
-      <c r="J90" s="12"/>
-      <c r="K90" s="16"/>
-      <c r="L90" s="16"/>
-      <c r="M90" s="11"/>
-      <c r="N90" s="11"/>
-      <c r="O90" s="11"/>
-      <c r="P90" s="16"/>
-      <c r="Q90" s="11"/>
-    </row>
-    <row r="91" spans="3:17">
-      <c r="C91" s="11"/>
-      <c r="D91" s="11"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="11"/>
-      <c r="G91" s="11"/>
-      <c r="H91" s="12"/>
-      <c r="I91" s="11"/>
-      <c r="J91" s="12"/>
-      <c r="K91" s="16"/>
-      <c r="L91" s="16"/>
-      <c r="M91" s="11"/>
-      <c r="N91" s="11"/>
-      <c r="O91" s="11"/>
-      <c r="P91" s="16"/>
-      <c r="Q91" s="11"/>
-    </row>
-    <row r="92" spans="3:17">
-      <c r="C92" s="11"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="11"/>
-      <c r="G92" s="11"/>
-      <c r="H92" s="12"/>
-      <c r="I92" s="11"/>
-      <c r="J92" s="12"/>
-      <c r="K92" s="16"/>
-      <c r="L92" s="16"/>
-      <c r="M92" s="11"/>
-      <c r="N92" s="11"/>
-      <c r="O92" s="11"/>
-      <c r="P92" s="16"/>
-      <c r="Q92" s="11"/>
-    </row>
-    <row r="93" spans="3:17">
-      <c r="C93" s="11"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="11"/>
-      <c r="F93" s="11"/>
-      <c r="G93" s="11"/>
-      <c r="H93" s="12"/>
-      <c r="I93" s="11"/>
-      <c r="J93" s="12"/>
-      <c r="K93" s="16"/>
-      <c r="L93" s="16"/>
-      <c r="M93" s="11"/>
-      <c r="N93" s="11"/>
-      <c r="O93" s="11"/>
-      <c r="P93" s="16"/>
-      <c r="Q93" s="11"/>
-    </row>
-    <row r="94" spans="3:17">
-      <c r="C94" s="11"/>
-      <c r="D94" s="11"/>
-      <c r="E94" s="11"/>
-      <c r="F94" s="11"/>
-      <c r="G94" s="11"/>
-      <c r="H94" s="12"/>
-      <c r="I94" s="11"/>
-      <c r="J94" s="12"/>
-      <c r="K94" s="16"/>
-      <c r="L94" s="16"/>
-      <c r="M94" s="11"/>
-      <c r="N94" s="11"/>
-      <c r="O94" s="11"/>
-      <c r="P94" s="16"/>
-      <c r="Q94" s="11"/>
-    </row>
-    <row r="95" spans="3:17">
-      <c r="C95" s="11"/>
-      <c r="D95" s="11"/>
-      <c r="E95" s="11"/>
-      <c r="F95" s="11"/>
-      <c r="G95" s="11"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="11"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="16"/>
-      <c r="L95" s="16"/>
-      <c r="M95" s="11"/>
-      <c r="N95" s="11"/>
-      <c r="O95" s="11"/>
-      <c r="P95" s="16"/>
-      <c r="Q95" s="11"/>
-    </row>
-    <row r="96" spans="3:17">
-      <c r="C96" s="11"/>
-      <c r="D96" s="11"/>
-      <c r="E96" s="11"/>
-      <c r="F96" s="11"/>
-      <c r="G96" s="11"/>
-      <c r="H96" s="12"/>
-      <c r="I96" s="11"/>
-      <c r="J96" s="12"/>
-      <c r="K96" s="16"/>
-      <c r="L96" s="16"/>
-      <c r="M96" s="11"/>
-      <c r="N96" s="11"/>
-      <c r="O96" s="11"/>
-      <c r="P96" s="16"/>
-      <c r="Q96" s="11"/>
-    </row>
-    <row r="97" spans="3:17">
-      <c r="C97" s="11"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="11"/>
-      <c r="G97" s="11"/>
-      <c r="H97" s="12"/>
-      <c r="I97" s="11"/>
-      <c r="J97" s="12"/>
-      <c r="K97" s="16"/>
-      <c r="L97" s="16"/>
-      <c r="M97" s="11"/>
-      <c r="N97" s="11"/>
-      <c r="O97" s="11"/>
-      <c r="P97" s="16"/>
-      <c r="Q97" s="11"/>
-    </row>
-    <row r="98" spans="3:17">
-      <c r="C98" s="11"/>
-      <c r="D98" s="11"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="11"/>
-      <c r="G98" s="11"/>
-      <c r="H98" s="12"/>
-      <c r="I98" s="11"/>
-      <c r="J98" s="12"/>
-      <c r="K98" s="16"/>
-      <c r="L98" s="16"/>
-      <c r="M98" s="11"/>
-      <c r="N98" s="11"/>
-      <c r="O98" s="11"/>
-      <c r="P98" s="16"/>
-      <c r="Q98" s="11"/>
-    </row>
-    <row r="99" spans="3:17">
-      <c r="C99" s="11"/>
-      <c r="D99" s="11"/>
-      <c r="E99" s="11"/>
-      <c r="F99" s="11"/>
-      <c r="G99" s="11"/>
-      <c r="H99" s="12"/>
-      <c r="I99" s="11"/>
-      <c r="J99" s="12"/>
-      <c r="K99" s="16"/>
-      <c r="L99" s="16"/>
-      <c r="M99" s="11"/>
-      <c r="N99" s="11"/>
-      <c r="O99" s="11"/>
-      <c r="P99" s="16"/>
-      <c r="Q99" s="11"/>
-    </row>
-    <row r="100" spans="3:17">
-      <c r="C100" s="11"/>
-      <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="11"/>
-      <c r="G100" s="11"/>
-      <c r="H100" s="12"/>
-      <c r="I100" s="11"/>
-      <c r="J100" s="12"/>
-      <c r="K100" s="16"/>
-      <c r="L100" s="16"/>
-      <c r="M100" s="11"/>
-      <c r="N100" s="11"/>
-      <c r="O100" s="11"/>
-      <c r="P100" s="16"/>
-      <c r="Q100" s="11"/>
-    </row>
-    <row r="101" spans="3:17">
-      <c r="C101" s="11"/>
-      <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="11"/>
-      <c r="G101" s="11"/>
-      <c r="H101" s="12"/>
-      <c r="I101" s="11"/>
-      <c r="J101" s="12"/>
-      <c r="K101" s="16"/>
-      <c r="L101" s="16"/>
-      <c r="M101" s="11"/>
-      <c r="N101" s="11"/>
-      <c r="O101" s="11"/>
-      <c r="P101" s="16"/>
-      <c r="Q101" s="11"/>
-    </row>
-    <row r="102" spans="3:17">
-      <c r="C102" s="11"/>
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="11"/>
-      <c r="G102" s="11"/>
-      <c r="H102" s="12"/>
-      <c r="I102" s="11"/>
-      <c r="J102" s="12"/>
-      <c r="K102" s="16"/>
-      <c r="L102" s="16"/>
-      <c r="M102" s="11"/>
-      <c r="N102" s="11"/>
-      <c r="O102" s="11"/>
-      <c r="P102" s="16"/>
-      <c r="Q102" s="11"/>
-    </row>
-    <row r="103" spans="3:17">
-      <c r="C103" s="11"/>
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="11"/>
-      <c r="G103" s="11"/>
-      <c r="H103" s="12"/>
-      <c r="I103" s="11"/>
-      <c r="J103" s="12"/>
-      <c r="K103" s="16"/>
-      <c r="L103" s="11"/>
-      <c r="M103" s="11"/>
-      <c r="N103" s="11"/>
-      <c r="O103" s="11"/>
-      <c r="P103" s="16"/>
-      <c r="Q103" s="11"/>
-    </row>
-    <row r="104" spans="3:17">
-      <c r="C104" s="11"/>
-      <c r="D104" s="11"/>
-      <c r="E104" s="11"/>
-      <c r="F104" s="11"/>
-      <c r="G104" s="11"/>
-      <c r="H104" s="12"/>
-      <c r="I104" s="11"/>
-      <c r="J104" s="12"/>
-      <c r="K104" s="16"/>
-      <c r="L104" s="16"/>
-      <c r="M104" s="11"/>
-      <c r="N104" s="11"/>
-      <c r="O104" s="11"/>
-      <c r="P104" s="16"/>
-      <c r="Q104" s="11"/>
-    </row>
-    <row r="105" spans="3:17">
-      <c r="C105" s="11"/>
-      <c r="D105" s="11"/>
-      <c r="E105" s="11"/>
-      <c r="F105" s="11"/>
-      <c r="G105" s="11"/>
-      <c r="H105" s="12"/>
-      <c r="I105" s="11"/>
-      <c r="J105" s="12"/>
-      <c r="K105" s="16"/>
-      <c r="L105" s="16"/>
-      <c r="M105" s="11"/>
-      <c r="N105" s="11"/>
-      <c r="O105" s="11"/>
-      <c r="P105" s="16"/>
-      <c r="Q105" s="11"/>
-    </row>
-    <row r="106" spans="3:17">
-      <c r="C106" s="11"/>
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="11"/>
-      <c r="G106" s="11"/>
-      <c r="H106" s="12"/>
-      <c r="I106" s="11"/>
-      <c r="J106" s="12"/>
-      <c r="K106" s="16"/>
-      <c r="L106" s="16"/>
-      <c r="M106" s="11"/>
-      <c r="N106" s="11"/>
-      <c r="O106" s="11"/>
-      <c r="P106" s="16"/>
-      <c r="Q106" s="11"/>
-    </row>
-    <row r="107" spans="3:17">
-      <c r="C107" s="11"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="11"/>
-      <c r="G107" s="11"/>
-      <c r="H107" s="12"/>
-      <c r="I107" s="11"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="16"/>
-      <c r="L107" s="16"/>
-      <c r="M107" s="11"/>
-      <c r="N107" s="11"/>
-      <c r="O107" s="11"/>
-      <c r="P107" s="16"/>
-      <c r="Q107" s="11"/>
-    </row>
-    <row r="108" spans="3:17">
-      <c r="C108" s="11"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
-      <c r="F108" s="11"/>
-      <c r="G108" s="11"/>
-      <c r="H108" s="12"/>
-      <c r="I108" s="11"/>
-      <c r="J108" s="12"/>
-      <c r="K108" s="16"/>
-      <c r="L108" s="16"/>
-      <c r="M108" s="11"/>
-      <c r="N108" s="11"/>
-      <c r="O108" s="11"/>
-      <c r="P108" s="16"/>
-      <c r="Q108" s="11"/>
-    </row>
-    <row r="109" spans="3:17">
-      <c r="C109" s="11"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="11"/>
-      <c r="F109" s="11"/>
-      <c r="G109" s="11"/>
-      <c r="H109" s="12"/>
-      <c r="I109" s="11"/>
-      <c r="J109" s="12"/>
-      <c r="K109" s="16"/>
-      <c r="L109" s="16"/>
-      <c r="M109" s="11"/>
-      <c r="N109" s="11"/>
-      <c r="O109" s="11"/>
-      <c r="P109" s="16"/>
-      <c r="Q109" s="11"/>
-    </row>
-    <row r="110" spans="3:17">
-      <c r="C110" s="11"/>
-      <c r="D110" s="11"/>
-      <c r="E110" s="11"/>
-      <c r="F110" s="11"/>
-      <c r="G110" s="11"/>
-      <c r="H110" s="12"/>
-      <c r="I110" s="11"/>
-      <c r="J110" s="12"/>
-      <c r="K110" s="16"/>
-      <c r="L110" s="16"/>
-      <c r="M110" s="11"/>
-      <c r="N110" s="11"/>
-      <c r="O110" s="11"/>
-      <c r="P110" s="16"/>
-      <c r="Q110" s="11"/>
-    </row>
-    <row r="111" spans="3:17">
-      <c r="C111" s="11"/>
-      <c r="D111" s="11"/>
-      <c r="E111" s="11"/>
-      <c r="F111" s="11"/>
-      <c r="G111" s="11"/>
-      <c r="H111" s="12"/>
-      <c r="I111" s="11"/>
-      <c r="J111" s="12"/>
-      <c r="K111" s="16"/>
-      <c r="L111" s="16"/>
-      <c r="M111" s="11"/>
-      <c r="N111" s="11"/>
-      <c r="O111" s="11"/>
-      <c r="P111" s="16"/>
-      <c r="Q111" s="11"/>
-    </row>
-    <row r="112" spans="3:17">
-      <c r="C112" s="11"/>
-      <c r="D112" s="11"/>
-      <c r="E112" s="11"/>
-      <c r="F112" s="11"/>
-      <c r="G112" s="11"/>
-      <c r="H112" s="12"/>
-      <c r="I112" s="11"/>
-      <c r="J112" s="12"/>
-      <c r="K112" s="16"/>
-      <c r="L112" s="16"/>
-      <c r="M112" s="11"/>
-      <c r="N112" s="11"/>
-      <c r="O112" s="11"/>
-      <c r="P112" s="16"/>
-      <c r="Q112" s="11"/>
-    </row>
-    <row r="113" spans="3:17">
-      <c r="C113" s="11"/>
-      <c r="D113" s="11"/>
-      <c r="E113" s="11"/>
-      <c r="F113" s="11"/>
-      <c r="G113" s="11"/>
-      <c r="H113" s="12"/>
-      <c r="I113" s="11"/>
-      <c r="J113" s="12"/>
-      <c r="K113" s="16"/>
-      <c r="L113" s="16"/>
-      <c r="M113" s="11"/>
-      <c r="N113" s="11"/>
-      <c r="O113" s="11"/>
-      <c r="P113" s="16"/>
-      <c r="Q113" s="11"/>
-    </row>
-    <row r="114" spans="3:17">
-      <c r="C114" s="11"/>
-      <c r="D114" s="11"/>
-      <c r="E114" s="11"/>
-      <c r="F114" s="11"/>
-      <c r="G114" s="11"/>
-      <c r="H114" s="12"/>
-      <c r="I114" s="11"/>
-      <c r="J114" s="12"/>
-      <c r="K114" s="16"/>
-      <c r="L114" s="16"/>
-      <c r="M114" s="11"/>
-      <c r="N114" s="11"/>
-      <c r="O114" s="11"/>
-      <c r="P114" s="16"/>
-      <c r="Q114" s="11"/>
-    </row>
-    <row r="115" spans="3:17">
-      <c r="C115" s="11"/>
-      <c r="D115" s="11"/>
-      <c r="E115" s="11"/>
-      <c r="F115" s="11"/>
-      <c r="G115" s="11"/>
-      <c r="H115" s="12"/>
-      <c r="I115" s="11"/>
-      <c r="J115" s="12"/>
-      <c r="K115" s="16"/>
-      <c r="L115" s="16"/>
-      <c r="M115" s="11"/>
-      <c r="N115" s="11"/>
-      <c r="O115" s="11"/>
-      <c r="P115" s="16"/>
-      <c r="Q115" s="11"/>
-    </row>
-    <row r="116" spans="3:17">
-      <c r="C116" s="11"/>
-      <c r="D116" s="11"/>
-      <c r="E116" s="11"/>
-      <c r="F116" s="11"/>
-      <c r="G116" s="11"/>
-      <c r="H116" s="12"/>
-      <c r="I116" s="11"/>
-      <c r="J116" s="12"/>
-      <c r="K116" s="16"/>
-      <c r="L116" s="16"/>
-      <c r="M116" s="11"/>
-      <c r="N116" s="11"/>
-      <c r="O116" s="11"/>
-      <c r="P116" s="16"/>
-      <c r="Q116" s="11"/>
-    </row>
-    <row r="117" spans="3:17">
-      <c r="C117" s="11"/>
-      <c r="D117" s="11"/>
-      <c r="E117" s="11"/>
-      <c r="F117" s="11"/>
-      <c r="G117" s="11"/>
-      <c r="H117" s="12"/>
-      <c r="I117" s="11"/>
-      <c r="J117" s="12"/>
-      <c r="K117" s="16"/>
-      <c r="L117" s="16"/>
-      <c r="M117" s="11"/>
-      <c r="N117" s="11"/>
-      <c r="O117" s="11"/>
-      <c r="P117" s="16"/>
-      <c r="Q117" s="11"/>
+    <row r="49" spans="2:17">
+      <c r="B49" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="5">
+        <v>0</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H49" s="5">
+        <v>8132908282</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="J49" s="6"/>
+      <c r="K49" s="9">
+        <v>39209</v>
+      </c>
+      <c r="L49" s="9">
+        <v>39209</v>
+      </c>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6">
+        <v>2</v>
+      </c>
+      <c r="P49" s="6"/>
+      <c r="Q49" s="5" t="s">
+        <v>228</v>
+      </c>
     </row>
   </sheetData>
   <sortState ref="C2:Q36">
